--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/90.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/90.xlsx
@@ -426,13 +426,13 @@
         <v>-12.43868872657282</v>
       </c>
       <c r="E2">
-        <v>-8.183253487852443</v>
+        <v>-5.917753039769125</v>
       </c>
       <c r="F2">
-        <v>3.343086140078559</v>
+        <v>3.700802546316614</v>
       </c>
       <c r="G2">
-        <v>-14.83339702120378</v>
+        <v>-14.62246892271465</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.84343060611859</v>
       </c>
       <c r="E3">
-        <v>-9.098951688469459</v>
+        <v>-5.387767612755432</v>
       </c>
       <c r="F3">
-        <v>3.351874124203333</v>
+        <v>3.221623814893931</v>
       </c>
       <c r="G3">
-        <v>-14.14507335849682</v>
+        <v>-13.31246618955181</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.15520567502497</v>
       </c>
       <c r="E4">
-        <v>-8.770030507396331</v>
+        <v>-6.786708331678967</v>
       </c>
       <c r="F4">
-        <v>3.312856361564651</v>
+        <v>3.88330723230594</v>
       </c>
       <c r="G4">
-        <v>-13.35385794042932</v>
+        <v>-12.85120456901962</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.43306310055619</v>
       </c>
       <c r="E5">
-        <v>-9.331244291166918</v>
+        <v>-7.956662233930643</v>
       </c>
       <c r="F5">
-        <v>3.401242988705327</v>
+        <v>3.963434833097599</v>
       </c>
       <c r="G5">
-        <v>-13.850145132767</v>
+        <v>-12.78974098053751</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.689176599434754</v>
       </c>
       <c r="E6">
-        <v>-11.3879594451266</v>
+        <v>-10.25932786819491</v>
       </c>
       <c r="F6">
-        <v>3.611122031443024</v>
+        <v>3.6890767877187</v>
       </c>
       <c r="G6">
-        <v>-12.12366914967276</v>
+        <v>-11.62845788463534</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.930333864107585</v>
       </c>
       <c r="E7">
-        <v>-11.51404574692216</v>
+        <v>-8.642766802358771</v>
       </c>
       <c r="F7">
-        <v>4.154936552392537</v>
+        <v>4.094964776786676</v>
       </c>
       <c r="G7">
-        <v>-12.08003284891963</v>
+        <v>-12.57066894002178</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.16800685739913</v>
       </c>
       <c r="E8">
-        <v>-12.16611430470864</v>
+        <v>-10.70010688573151</v>
       </c>
       <c r="F8">
-        <v>4.033727620154379</v>
+        <v>4.107776957642581</v>
       </c>
       <c r="G8">
-        <v>-10.8149045605416</v>
+        <v>-10.72425851313082</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.394141936280348</v>
       </c>
       <c r="E9">
-        <v>-13.08927090201629</v>
+        <v>-11.64078867744884</v>
       </c>
       <c r="F9">
-        <v>3.903152651132312</v>
+        <v>4.730277907000703</v>
       </c>
       <c r="G9">
-        <v>-9.920858632206029</v>
+        <v>-9.550838957281687</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.614244246316235</v>
       </c>
       <c r="E10">
-        <v>-14.22962669815383</v>
+        <v>-10.88881292610514</v>
       </c>
       <c r="F10">
-        <v>4.343997780871783</v>
+        <v>4.6655423440012</v>
       </c>
       <c r="G10">
-        <v>-9.688335845164238</v>
+        <v>-9.229669692334832</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.816272479849764</v>
       </c>
       <c r="E11">
-        <v>-14.32908557278429</v>
+        <v>-12.05582332025183</v>
       </c>
       <c r="F11">
-        <v>4.336738072955408</v>
+        <v>4.631898095533605</v>
       </c>
       <c r="G11">
-        <v>-7.601497048483713</v>
+        <v>-7.4832741567308</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.009140656960555</v>
       </c>
       <c r="E12">
-        <v>-15.04638227017725</v>
+        <v>-14.3246612536788</v>
       </c>
       <c r="F12">
-        <v>4.040220814407681</v>
+        <v>4.742475609961417</v>
       </c>
       <c r="G12">
-        <v>-6.890322345191938</v>
+        <v>-6.840637677738555</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.187599961940784</v>
       </c>
       <c r="E13">
-        <v>-15.08395501901889</v>
+        <v>-12.36482374416521</v>
       </c>
       <c r="F13">
-        <v>4.456659452284314</v>
+        <v>4.606014006051662</v>
       </c>
       <c r="G13">
-        <v>-6.545833597466456</v>
+        <v>-6.12223936408009</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.36957136059295</v>
       </c>
       <c r="E14">
-        <v>-16.03062345337437</v>
+        <v>-13.88338863247537</v>
       </c>
       <c r="F14">
-        <v>4.258447571025659</v>
+        <v>5.071205446829183</v>
       </c>
       <c r="G14">
-        <v>-6.338609999435776</v>
+        <v>-6.092106778581644</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.559015733626966</v>
       </c>
       <c r="E15">
-        <v>-17.26457827877645</v>
+        <v>-16.29990010329247</v>
       </c>
       <c r="F15">
-        <v>4.701380025161679</v>
+        <v>4.97271635965392</v>
       </c>
       <c r="G15">
-        <v>-5.300144832495033</v>
+        <v>-4.280092919843717</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.77951772622263</v>
       </c>
       <c r="E16">
-        <v>-18.35267548486548</v>
+        <v>-17.57008724922992</v>
       </c>
       <c r="F16">
-        <v>4.589187130700118</v>
+        <v>4.770611729255115</v>
       </c>
       <c r="G16">
-        <v>-5.021592220275216</v>
+        <v>-3.891315693893865</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.041358182982757</v>
       </c>
       <c r="E17">
-        <v>-18.64653722017122</v>
+        <v>-17.68890987871718</v>
       </c>
       <c r="F17">
-        <v>4.432232372244576</v>
+        <v>4.938120303931145</v>
       </c>
       <c r="G17">
-        <v>-4.138822010046397</v>
+        <v>-3.508742430284608</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.3704401072394458</v>
       </c>
       <c r="E18">
-        <v>-19.81242002429</v>
+        <v>-18.22937419458463</v>
       </c>
       <c r="F18">
-        <v>4.91428236249195</v>
+        <v>4.99687896080578</v>
       </c>
       <c r="G18">
-        <v>-3.622678165564166</v>
+        <v>-3.109295316061686</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2191209714035335</v>
       </c>
       <c r="E19">
-        <v>-20.86097459534405</v>
+        <v>-18.05239690189086</v>
       </c>
       <c r="F19">
-        <v>4.983081714870471</v>
+        <v>5.567747929908744</v>
       </c>
       <c r="G19">
-        <v>-3.265927157161224</v>
+        <v>-2.550180590479715</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7010810209356521</v>
       </c>
       <c r="E20">
-        <v>-21.3186719917733</v>
+        <v>-20.07430167615357</v>
       </c>
       <c r="F20">
-        <v>4.893055952107316</v>
+        <v>5.829697639440176</v>
       </c>
       <c r="G20">
-        <v>-2.944095783106515</v>
+        <v>-2.171159542234096</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.062721054766819</v>
       </c>
       <c r="E21">
-        <v>-21.07957762111632</v>
+        <v>-20.02993168782642</v>
       </c>
       <c r="F21">
-        <v>5.19936368062429</v>
+        <v>4.72052069485568</v>
       </c>
       <c r="G21">
-        <v>-2.858322858729538</v>
+        <v>-2.864202387607283</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.285620660707109</v>
       </c>
       <c r="E22">
-        <v>-22.65387896751288</v>
+        <v>-20.21927171456113</v>
       </c>
       <c r="F22">
-        <v>5.000744786945368</v>
+        <v>5.288865236729435</v>
       </c>
       <c r="G22">
-        <v>-2.504826116591699</v>
+        <v>-0.9772477094968741</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.367435534242051</v>
       </c>
       <c r="E23">
-        <v>-22.75792971478712</v>
+        <v>-20.44036087256361</v>
       </c>
       <c r="F23">
-        <v>4.761114244880225</v>
+        <v>5.311564493615428</v>
       </c>
       <c r="G23">
-        <v>-2.243279776807118</v>
+        <v>-1.809492373705336</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.304076285618126</v>
       </c>
       <c r="E24">
-        <v>-22.62636395944227</v>
+        <v>-22.0555316968794</v>
       </c>
       <c r="F24">
-        <v>4.544015086874039</v>
+        <v>5.270380221284426</v>
       </c>
       <c r="G24">
-        <v>-2.265073098092141</v>
+        <v>-1.646961140454817</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.107564828022028</v>
       </c>
       <c r="E25">
-        <v>-23.93535559915145</v>
+        <v>-22.54650884879101</v>
       </c>
       <c r="F25">
-        <v>4.621737038380145</v>
+        <v>4.925444321783968</v>
       </c>
       <c r="G25">
-        <v>-1.572768504374211</v>
+        <v>-1.106471544076786</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.7883818060364514</v>
       </c>
       <c r="E26">
-        <v>-23.46788122733964</v>
+        <v>-23.74698013738038</v>
       </c>
       <c r="F26">
-        <v>4.363966728759559</v>
+        <v>4.745261348666675</v>
       </c>
       <c r="G26">
-        <v>-1.193820288130456</v>
+        <v>-0.4490303054329207</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.3694891483338306</v>
       </c>
       <c r="E27">
-        <v>-23.65712615612019</v>
+        <v>-22.2063162959128</v>
       </c>
       <c r="F27">
-        <v>4.431758844175859</v>
+        <v>4.633296507856937</v>
       </c>
       <c r="G27">
-        <v>-1.242882573022455</v>
+        <v>-1.277477773907839</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.1314229488777219</v>
       </c>
       <c r="E28">
-        <v>-24.24305635102464</v>
+        <v>-21.85986086348197</v>
       </c>
       <c r="F28">
-        <v>4.502496652594878</v>
+        <v>4.947915525018138</v>
       </c>
       <c r="G28">
-        <v>-1.56232373319781</v>
+        <v>-0.4840658088750276</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.6909239438351891</v>
       </c>
       <c r="E29">
-        <v>-23.28295193428841</v>
+        <v>-21.82331154976606</v>
       </c>
       <c r="F29">
-        <v>4.20652102147023</v>
+        <v>4.367564908599437</v>
       </c>
       <c r="G29">
-        <v>-1.405450222273906</v>
+        <v>-0.02414495928623868</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.294584453720495</v>
       </c>
       <c r="E30">
-        <v>-23.41680456900713</v>
+        <v>-22.1282137047025</v>
       </c>
       <c r="F30">
-        <v>4.553504652719352</v>
+        <v>4.907063830929378</v>
       </c>
       <c r="G30">
-        <v>-1.657677376365438</v>
+        <v>-1.267685180202675</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.925328500145714</v>
       </c>
       <c r="E31">
-        <v>-21.91701473393277</v>
+        <v>-22.28632537468032</v>
       </c>
       <c r="F31">
-        <v>4.576731283675187</v>
+        <v>4.851763987774063</v>
       </c>
       <c r="G31">
-        <v>-1.362293950623967</v>
+        <v>-1.166918795078338</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.575130515929433</v>
       </c>
       <c r="E32">
-        <v>-22.3749340255884</v>
+        <v>-22.33063649284537</v>
       </c>
       <c r="F32">
-        <v>4.455501763260128</v>
+        <v>4.833456347391583</v>
       </c>
       <c r="G32">
-        <v>-1.869333794873202</v>
+        <v>-1.149763548093835</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.232265164207638</v>
       </c>
       <c r="E33">
-        <v>-22.38636389398376</v>
+        <v>-21.95778005694982</v>
       </c>
       <c r="F33">
-        <v>4.3740438494995</v>
+        <v>4.581675613543188</v>
       </c>
       <c r="G33">
-        <v>-1.857154297834224</v>
+        <v>-2.627673840462974</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.891470688929593</v>
       </c>
       <c r="E34">
-        <v>-21.64302394257269</v>
+        <v>-21.26499146088637</v>
       </c>
       <c r="F34">
-        <v>4.274207028590197</v>
+        <v>4.97428581221612</v>
       </c>
       <c r="G34">
-        <v>-2.090041244885334</v>
+        <v>-1.402242303646352</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.541511995818727</v>
       </c>
       <c r="E35">
-        <v>-20.594682209797</v>
+        <v>-19.49080780026525</v>
       </c>
       <c r="F35">
-        <v>4.792251486883679</v>
+        <v>4.901335566633233</v>
       </c>
       <c r="G35">
-        <v>-2.457210540100362</v>
+        <v>-1.557808149082244</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.17692196143479</v>
       </c>
       <c r="E36">
-        <v>-19.54034477743516</v>
+        <v>-20.29819848804081</v>
       </c>
       <c r="F36">
-        <v>4.870351944103576</v>
+        <v>5.165662418743739</v>
       </c>
       <c r="G36">
-        <v>-2.591247907894374</v>
+        <v>-1.936256472949569</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.786997638689557</v>
       </c>
       <c r="E37">
-        <v>-20.10450659778474</v>
+        <v>-19.57167728909423</v>
       </c>
       <c r="F37">
-        <v>4.696842707713945</v>
+        <v>4.98192244214037</v>
       </c>
       <c r="G37">
-        <v>-3.122835447317305</v>
+        <v>-3.149452233453046</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.368199781097698</v>
       </c>
       <c r="E38">
-        <v>-19.53808054043132</v>
+        <v>-17.78412104472845</v>
       </c>
       <c r="F38">
-        <v>5.200427930999465</v>
+        <v>5.33243457016909</v>
       </c>
       <c r="G38">
-        <v>-3.483529315457519</v>
+        <v>-2.140729007637115</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.913053477653482</v>
       </c>
       <c r="E39">
-        <v>-18.044807179454</v>
+        <v>-18.02627666381462</v>
       </c>
       <c r="F39">
-        <v>5.215793045791059</v>
+        <v>5.69764982391675</v>
       </c>
       <c r="G39">
-        <v>-3.540742163467204</v>
+        <v>-3.446242641048708</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.42251984477195</v>
       </c>
       <c r="E40">
-        <v>-17.87103604635767</v>
+        <v>-17.41193935146005</v>
       </c>
       <c r="F40">
-        <v>5.454549382190879</v>
+        <v>5.681960049412491</v>
       </c>
       <c r="G40">
-        <v>-3.164707227298007</v>
+        <v>-2.298489744765544</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.893674685715082</v>
       </c>
       <c r="E41">
-        <v>-17.53639993108686</v>
+        <v>-17.04419556271916</v>
       </c>
       <c r="F41">
-        <v>5.226646182429565</v>
+        <v>5.633812222171301</v>
       </c>
       <c r="G41">
-        <v>-3.671909288278667</v>
+        <v>-3.863987140467182</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.331292014465816</v>
       </c>
       <c r="E42">
-        <v>-17.14930144443719</v>
+        <v>-15.78073772915711</v>
       </c>
       <c r="F42">
-        <v>5.336249717719383</v>
+        <v>6.183006592115562</v>
       </c>
       <c r="G42">
-        <v>-4.082605636244033</v>
+        <v>-3.863172746264521</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.734512006519928</v>
       </c>
       <c r="E43">
-        <v>-15.38184709619147</v>
+        <v>-15.37314789762273</v>
       </c>
       <c r="F43">
-        <v>5.362650095329759</v>
+        <v>6.247803919645767</v>
       </c>
       <c r="G43">
-        <v>-4.611557981417705</v>
+        <v>-3.860842122204874</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.107582158340554</v>
       </c>
       <c r="E44">
-        <v>-15.16592492703174</v>
+        <v>-15.06094131411191</v>
       </c>
       <c r="F44">
-        <v>5.499119617769091</v>
+        <v>6.038214695090595</v>
       </c>
       <c r="G44">
-        <v>-5.550147299984175</v>
+        <v>-3.984484377005574</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.44822765928682</v>
       </c>
       <c r="E45">
-        <v>-14.86973102761204</v>
+        <v>-15.73490504372548</v>
       </c>
       <c r="F45">
-        <v>5.701601170175771</v>
+        <v>6.043458345376615</v>
       </c>
       <c r="G45">
-        <v>-5.171351368835227</v>
+        <v>-3.255959104542478</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.758287245188212</v>
       </c>
       <c r="E46">
-        <v>-14.539089026416</v>
+        <v>-13.35784110998919</v>
       </c>
       <c r="F46">
-        <v>5.457401636544586</v>
+        <v>5.679548065303277</v>
       </c>
       <c r="G46">
-        <v>-5.089501440922286</v>
+        <v>-4.149822952873396</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.03413767171516</v>
       </c>
       <c r="E47">
-        <v>-14.23782776458172</v>
+        <v>-14.45703307739701</v>
       </c>
       <c r="F47">
-        <v>5.842888326009871</v>
+        <v>5.853426305171205</v>
       </c>
       <c r="G47">
-        <v>-5.264076438844674</v>
+        <v>-5.170987208825907</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.27669398568142</v>
       </c>
       <c r="E48">
-        <v>-13.28034533429593</v>
+        <v>-12.7910165469231</v>
       </c>
       <c r="F48">
-        <v>5.958456097777233</v>
+        <v>6.109418113048752</v>
       </c>
       <c r="G48">
-        <v>-5.959469771550744</v>
+        <v>-5.286783470698535</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.48418059343736</v>
       </c>
       <c r="E49">
-        <v>-12.32341537783908</v>
+        <v>-13.44193940078564</v>
       </c>
       <c r="F49">
-        <v>5.712669690818777</v>
+        <v>6.345745044574288</v>
       </c>
       <c r="G49">
-        <v>-5.189668617304014</v>
+        <v>-5.100575215751149</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.65935622426845</v>
       </c>
       <c r="E50">
-        <v>-12.8190568579786</v>
+        <v>-13.25736785718101</v>
       </c>
       <c r="F50">
-        <v>5.919357566136864</v>
+        <v>6.166642158891326</v>
       </c>
       <c r="G50">
-        <v>-6.492335181551834</v>
+        <v>-4.756745266587982</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.80284015065171</v>
       </c>
       <c r="E51">
-        <v>-10.83607884628582</v>
+        <v>-11.64488694642578</v>
       </c>
       <c r="F51">
-        <v>5.886896345988102</v>
+        <v>6.295158310223322</v>
       </c>
       <c r="G51">
-        <v>-6.436823953949334</v>
+        <v>-5.372668953623847</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.91695406503267</v>
       </c>
       <c r="E52">
-        <v>-10.9663675719605</v>
+        <v>-10.50523306375943</v>
       </c>
       <c r="F52">
-        <v>5.85362585211655</v>
+        <v>6.372935691436468</v>
       </c>
       <c r="G52">
-        <v>-6.353000940894988</v>
+        <v>-5.517578152968825</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.0027416667923</v>
       </c>
       <c r="E53">
-        <v>-11.81716821157359</v>
+        <v>-12.03780905064932</v>
       </c>
       <c r="F53">
-        <v>6.003605969720496</v>
+        <v>6.377754908537151</v>
       </c>
       <c r="G53">
-        <v>-6.303822786909114</v>
+        <v>-5.242233459376562</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.06175011652928</v>
       </c>
       <c r="E54">
-        <v>-9.262606210632658</v>
+        <v>-10.91273685428766</v>
       </c>
       <c r="F54">
-        <v>5.706889164227423</v>
+        <v>6.278766953998524</v>
       </c>
       <c r="G54">
-        <v>-7.583103657467523</v>
+        <v>-5.302876032564932</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.09591117395064</v>
       </c>
       <c r="E55">
-        <v>-9.602354973058127</v>
+        <v>-9.102701264947811</v>
       </c>
       <c r="F55">
-        <v>5.899189071303743</v>
+        <v>6.189601143547452</v>
       </c>
       <c r="G55">
-        <v>-7.474127119405793</v>
+        <v>-5.825346329572711</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.10579060085942</v>
       </c>
       <c r="E56">
-        <v>-9.011506855381345</v>
+        <v>-9.426867548312885</v>
       </c>
       <c r="F56">
-        <v>5.964466261726326</v>
+        <v>6.332709561184307</v>
       </c>
       <c r="G56">
-        <v>-7.373039611364147</v>
+        <v>-5.156731999733806</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.09356419660477</v>
       </c>
       <c r="E57">
-        <v>-8.66453970538765</v>
+        <v>-8.79720587991636</v>
       </c>
       <c r="F57">
-        <v>6.07847091575515</v>
+        <v>6.445334807360783</v>
       </c>
       <c r="G57">
-        <v>-7.266658541005207</v>
+        <v>-6.013037708921691</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.05869502746094</v>
       </c>
       <c r="E58">
-        <v>-8.169314844856835</v>
+        <v>-9.999379874732611</v>
       </c>
       <c r="F58">
-        <v>5.908601035559199</v>
+        <v>6.288587514380163</v>
       </c>
       <c r="G58">
-        <v>-7.205333995435748</v>
+        <v>-7.353960937421328</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.00513071637627</v>
       </c>
       <c r="E59">
-        <v>-7.360918835851568</v>
+        <v>-7.897832828096996</v>
       </c>
       <c r="F59">
-        <v>6.075075450272448</v>
+        <v>6.485264784606757</v>
       </c>
       <c r="G59">
-        <v>-6.871736942534469</v>
+        <v>-6.439512116927222</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.93367904502914</v>
       </c>
       <c r="E60">
-        <v>-7.722345403351755</v>
+        <v>-6.072708363363589</v>
       </c>
       <c r="F60">
-        <v>5.959202023263406</v>
+        <v>5.958060171298373</v>
       </c>
       <c r="G60">
-        <v>-7.716541816518926</v>
+        <v>-6.776217772089877</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.85039970470618</v>
       </c>
       <c r="E61">
-        <v>-8.027215858970147</v>
+        <v>-6.335839874053283</v>
       </c>
       <c r="F61">
-        <v>6.09007631270349</v>
+        <v>5.963402011351151</v>
       </c>
       <c r="G61">
-        <v>-7.349177199117081</v>
+        <v>-7.073157154234806</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.75481585149513</v>
       </c>
       <c r="E62">
-        <v>-7.877780745191033</v>
+        <v>-7.664706986182127</v>
       </c>
       <c r="F62">
-        <v>6.053788859063026</v>
+        <v>5.991804193238642</v>
       </c>
       <c r="G62">
-        <v>-7.748885846437606</v>
+        <v>-7.666651895242109</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.65266055716171</v>
       </c>
       <c r="E63">
-        <v>-7.717563334799655</v>
+        <v>-7.888925319723909</v>
       </c>
       <c r="F63">
-        <v>5.788234634868055</v>
+        <v>6.182469715810228</v>
       </c>
       <c r="G63">
-        <v>-7.640740255306234</v>
+        <v>-7.376105176533513</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.54140584591467</v>
       </c>
       <c r="E64">
-        <v>-6.637114721309585</v>
+        <v>-6.674415761710765</v>
       </c>
       <c r="F64">
-        <v>5.756850334741792</v>
+        <v>6.570770650687249</v>
       </c>
       <c r="G64">
-        <v>-7.751385308319755</v>
+        <v>-7.53955343089841</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.42655253149622</v>
       </c>
       <c r="E65">
-        <v>-6.477662623025504</v>
+        <v>-7.080674221886889</v>
       </c>
       <c r="F65">
-        <v>5.783355236942587</v>
+        <v>6.114302262091968</v>
       </c>
       <c r="G65">
-        <v>-8.105249521012452</v>
+        <v>-7.923685961456663</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.30406811440442</v>
       </c>
       <c r="E66">
-        <v>-7.037608434073944</v>
+        <v>-6.127394215480217</v>
       </c>
       <c r="F66">
-        <v>5.964486849903227</v>
+        <v>6.341711345607664</v>
       </c>
       <c r="G66">
-        <v>-7.83676096723202</v>
+        <v>-6.971096345804615</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.17904330449106</v>
       </c>
       <c r="E67">
-        <v>-7.129495700163583</v>
+        <v>-6.411465389981378</v>
       </c>
       <c r="F67">
-        <v>5.788321738693404</v>
+        <v>6.226587011496624</v>
       </c>
       <c r="G67">
-        <v>-8.229312215096639</v>
+        <v>-7.712307628774198</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.04552089337817</v>
       </c>
       <c r="E68">
-        <v>-7.184349105818494</v>
+        <v>-6.330396648296063</v>
       </c>
       <c r="F68">
-        <v>5.873962219776708</v>
+        <v>5.673962334539522</v>
       </c>
       <c r="G68">
-        <v>-8.07682186646673</v>
+        <v>-7.506567155145111</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.908125641658684</v>
       </c>
       <c r="E69">
-        <v>-7.079148126146303</v>
+        <v>-7.147989988010909</v>
       </c>
       <c r="F69">
-        <v>5.655184333500157</v>
+        <v>6.151731567697463</v>
       </c>
       <c r="G69">
-        <v>-7.95445086115311</v>
+        <v>-7.22898784331384</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.760614882611145</v>
       </c>
       <c r="E70">
-        <v>-6.780142044367845</v>
+        <v>-5.820268579806005</v>
       </c>
       <c r="F70">
-        <v>5.258122337498924</v>
+        <v>5.439770238587998</v>
       </c>
       <c r="G70">
-        <v>-7.796200163284869</v>
+        <v>-7.257885595326139</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.609937848965316</v>
       </c>
       <c r="E71">
-        <v>-6.63100128139923</v>
+        <v>-6.61094014154525</v>
       </c>
       <c r="F71">
-        <v>5.400625779476082</v>
+        <v>6.097624255096475</v>
       </c>
       <c r="G71">
-        <v>-7.768070457837682</v>
+        <v>-7.621876766823466</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.450547346397496</v>
       </c>
       <c r="E72">
-        <v>-7.856664470893266</v>
+        <v>-6.634076115250438</v>
       </c>
       <c r="F72">
-        <v>5.18192074367164</v>
+        <v>5.918819106125615</v>
       </c>
       <c r="G72">
-        <v>-7.328953076417673</v>
+        <v>-6.961605011743525</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.289299334066181</v>
       </c>
       <c r="E73">
-        <v>-7.897583762026575</v>
+        <v>-6.68704114724415</v>
       </c>
       <c r="F73">
-        <v>5.139110005365481</v>
+        <v>5.666973440334687</v>
       </c>
       <c r="G73">
-        <v>-7.591691212596392</v>
+        <v>-7.232053408483206</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.118702243690514</v>
       </c>
       <c r="E74">
-        <v>-6.848648799155883</v>
+        <v>-6.423275650193383</v>
       </c>
       <c r="F74">
-        <v>5.351279086856904</v>
+        <v>5.558239359592446</v>
       </c>
       <c r="G74">
-        <v>-6.895735087148646</v>
+        <v>-6.388069549792488</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.943419159520323</v>
       </c>
       <c r="E75">
-        <v>-8.075715815592297</v>
+        <v>-7.414046892909557</v>
       </c>
       <c r="F75">
-        <v>5.274608716078649</v>
+        <v>5.820735447664704</v>
       </c>
       <c r="G75">
-        <v>-6.716919280390452</v>
+        <v>-6.945353543691242</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.753029354343482</v>
       </c>
       <c r="E76">
-        <v>-7.61962149896176</v>
+        <v>-7.773947364669159</v>
       </c>
       <c r="F76">
-        <v>4.909436222390706</v>
+        <v>5.53590910618475</v>
       </c>
       <c r="G76">
-        <v>-7.141261697068694</v>
+        <v>-7.144883433888656</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.548975246783225</v>
       </c>
       <c r="E77">
-        <v>-8.849392014380754</v>
+        <v>-7.32878478429314</v>
       </c>
       <c r="F77">
-        <v>4.897013633189998</v>
+        <v>5.124734706771037</v>
       </c>
       <c r="G77">
-        <v>-7.300343341867292</v>
+        <v>-5.809972156088335</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.317531900026669</v>
       </c>
       <c r="E78">
-        <v>-9.872175039857151</v>
+        <v>-8.470784416495466</v>
       </c>
       <c r="F78">
-        <v>4.869192671373474</v>
+        <v>5.261478210333741</v>
       </c>
       <c r="G78">
-        <v>-6.375721214931006</v>
+        <v>-6.372801313765369</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.058321395324743</v>
       </c>
       <c r="E79">
-        <v>-9.771683673152937</v>
+        <v>-10.51259183402189</v>
       </c>
       <c r="F79">
-        <v>4.797579073583218</v>
+        <v>5.230542098981546</v>
       </c>
       <c r="G79">
-        <v>-6.87509383571129</v>
+        <v>-5.779756806951407</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.758303334845349</v>
       </c>
       <c r="E80">
-        <v>-10.1392372659855</v>
+        <v>-9.449020843158408</v>
       </c>
       <c r="F80">
-        <v>4.712218908446947</v>
+        <v>5.005883912640968</v>
       </c>
       <c r="G80">
-        <v>-6.139927608896416</v>
+        <v>-5.186980454326126</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.41890572202687</v>
       </c>
       <c r="E81">
-        <v>-10.71534067229331</v>
+        <v>-10.79781776939501</v>
       </c>
       <c r="F81">
-        <v>4.931698376444039</v>
+        <v>4.97893557278385</v>
       </c>
       <c r="G81">
-        <v>-6.019873985460285</v>
+        <v>-5.060103796533558</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.030765584332387</v>
       </c>
       <c r="E82">
-        <v>-11.75090757989336</v>
+        <v>-11.78957169097085</v>
       </c>
       <c r="F82">
-        <v>4.600624654821422</v>
+        <v>4.97961656632749</v>
       </c>
       <c r="G82">
-        <v>-5.607442911632342</v>
+        <v>-5.686134579100818</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.59970901714348</v>
       </c>
       <c r="E83">
-        <v>-13.20300805519294</v>
+        <v>-10.42938112413095</v>
       </c>
       <c r="F83">
-        <v>4.450554265980295</v>
+        <v>4.786399693526131</v>
       </c>
       <c r="G83">
-        <v>-5.075944756938971</v>
+        <v>-5.036618786477968</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.121868249042921</v>
       </c>
       <c r="E84">
-        <v>-13.38056499255968</v>
+        <v>-13.2697034203779</v>
       </c>
       <c r="F84">
-        <v>4.532243400804577</v>
+        <v>4.7732976944877</v>
       </c>
       <c r="G84">
-        <v>-4.879990255923969</v>
+        <v>-4.959228163406426</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.608948095010693</v>
       </c>
       <c r="E85">
-        <v>-15.61835117971606</v>
+        <v>-14.51275142158739</v>
       </c>
       <c r="F85">
-        <v>4.390452626489368</v>
+        <v>4.5410979005778</v>
       </c>
       <c r="G85">
-        <v>-4.890941540567879</v>
+        <v>-4.921021157337697</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.064488374442323</v>
       </c>
       <c r="E86">
-        <v>-16.09634519664769</v>
+        <v>-16.46146247046413</v>
       </c>
       <c r="F86">
-        <v>4.179746889263812</v>
+        <v>4.570117727772312</v>
       </c>
       <c r="G86">
-        <v>-4.82411817885769</v>
+        <v>-4.162856570661506</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.507937578783454</v>
       </c>
       <c r="E87">
-        <v>-17.06067920810708</v>
+        <v>-16.70193802569344</v>
       </c>
       <c r="F87">
-        <v>4.313924789243503</v>
+        <v>4.715549441987116</v>
       </c>
       <c r="G87">
-        <v>-3.89488115143966</v>
+        <v>-3.812600852606614</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.949180553168509</v>
       </c>
       <c r="E88">
-        <v>-18.20572650331657</v>
+        <v>-17.57383229723427</v>
       </c>
       <c r="F88">
-        <v>3.895357650616519</v>
+        <v>4.343611356628416</v>
       </c>
       <c r="G88">
-        <v>-3.919385809521346</v>
+        <v>-3.678325125533775</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.4113194400853</v>
       </c>
       <c r="E89">
-        <v>-20.33593879042074</v>
+        <v>-20.269967981077</v>
       </c>
       <c r="F89">
-        <v>3.876883721112918</v>
+        <v>4.574544185805965</v>
       </c>
       <c r="G89">
-        <v>-3.401278811534326</v>
+        <v>-3.131714330453631</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.90535262579632</v>
       </c>
       <c r="E90">
-        <v>-21.41123852896409</v>
+        <v>-21.164998226323</v>
       </c>
       <c r="F90">
-        <v>3.75895622753155</v>
+        <v>4.409895784013218</v>
       </c>
       <c r="G90">
-        <v>-3.542132592593698</v>
+        <v>-2.651115813426554</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.453005572936741</v>
       </c>
       <c r="E91">
-        <v>-22.95101931800018</v>
+        <v>-23.94540881144848</v>
       </c>
       <c r="F91">
-        <v>3.606698740821202</v>
+        <v>4.067623677862529</v>
       </c>
       <c r="G91">
-        <v>-2.829944862366905</v>
+        <v>-2.05067554787786</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.061844808561883</v>
       </c>
       <c r="E92">
-        <v>-24.7855403662995</v>
+        <v>-24.90434488189073</v>
       </c>
       <c r="F92">
-        <v>3.344703103818223</v>
+        <v>3.584631382595469</v>
       </c>
       <c r="G92">
-        <v>-2.520667076997112</v>
+        <v>-1.218857944043964</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.747887852289715</v>
       </c>
       <c r="E93">
-        <v>-28.44597836228357</v>
+        <v>-27.74504304148033</v>
       </c>
       <c r="F93">
-        <v>3.159369919063922</v>
+        <v>3.750868241421401</v>
       </c>
       <c r="G93">
-        <v>-2.493911247948722</v>
+        <v>-1.461924818628333</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.511076665179471</v>
       </c>
       <c r="E94">
-        <v>-29.85325600185523</v>
+        <v>-30.2379928893099</v>
       </c>
       <c r="F94">
-        <v>2.772912417872472</v>
+        <v>3.361210070574848</v>
       </c>
       <c r="G94">
-        <v>-1.998743020003313</v>
+        <v>-1.846001069912419</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.356613207618424</v>
       </c>
       <c r="E95">
-        <v>-31.4450395221584</v>
+        <v>-30.85083806947894</v>
       </c>
       <c r="F95">
-        <v>2.230508978893616</v>
+        <v>3.169125547503029</v>
       </c>
       <c r="G95">
-        <v>-2.690276256610593</v>
+        <v>-1.339441254766378</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.273163083810485</v>
       </c>
       <c r="E96">
-        <v>-33.44439476009993</v>
+        <v>-34.52453770159448</v>
       </c>
       <c r="F96">
-        <v>2.030840088192757</v>
+        <v>2.799719807903116</v>
       </c>
       <c r="G96">
-        <v>-1.773599438968558</v>
+        <v>-0.3618404675651354</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.252766441474096</v>
       </c>
       <c r="E97">
-        <v>-36.00197272472997</v>
+        <v>-36.78070722898499</v>
       </c>
       <c r="F97">
-        <v>1.87255343306233</v>
+        <v>2.517140745117171</v>
       </c>
       <c r="G97">
-        <v>-1.600994215642037</v>
+        <v>-1.064404441909267</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.272509497003146</v>
       </c>
       <c r="E98">
-        <v>-38.70440978015437</v>
+        <v>-39.05455591890145</v>
       </c>
       <c r="F98">
-        <v>1.313421308498687</v>
+        <v>2.56134039351117</v>
       </c>
       <c r="G98">
-        <v>-1.779349856570272</v>
+        <v>-1.119647515323085</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.312592501440293</v>
       </c>
       <c r="E99">
-        <v>-40.28676728181058</v>
+        <v>-41.07445684341577</v>
       </c>
       <c r="F99">
-        <v>1.247132129996138</v>
+        <v>1.794612930139893</v>
       </c>
       <c r="G99">
-        <v>-2.245021123760775</v>
+        <v>-0.6544960037822476</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.344039489977262</v>
       </c>
       <c r="E100">
-        <v>-43.16026744287473</v>
+        <v>-43.96149034905184</v>
       </c>
       <c r="F100">
-        <v>0.7738036082250886</v>
+        <v>1.41338640958714</v>
       </c>
       <c r="G100">
-        <v>-2.256161109500423</v>
+        <v>-2.555494016070245</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.345981683967478</v>
       </c>
       <c r="E101">
-        <v>-45.33882571848478</v>
+        <v>-44.25062662173058</v>
       </c>
       <c r="F101">
-        <v>0.534867521203866</v>
+        <v>1.555425825731074</v>
       </c>
       <c r="G101">
-        <v>-3.165601074593611</v>
+        <v>-1.051334408120224</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.29485474782863</v>
       </c>
       <c r="E102">
-        <v>-47.20323922370874</v>
+        <v>-48.94375254796433</v>
       </c>
       <c r="F102">
-        <v>0.5340099444506556</v>
+        <v>0.6676446333013516</v>
       </c>
       <c r="G102">
-        <v>-2.604824455150925</v>
+        <v>-1.345446584374616</v>
       </c>
     </row>
   </sheetData>
